--- a/KAMCHATKA_REESTR_POSTAVSHIKI/01_ДН_РУ_реестр.xlsx
+++ b/KAMCHATKA_REESTR_POSTAVSHIKI/01_ДН_РУ_реестр.xlsx
@@ -38,7 +38,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -112,6 +117,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6026,12 +6034,36 @@
       <c r="H130" s="7" t="n">
         <v>6150.02</v>
       </c>
-      <c r="I130" s="8" t="n"/>
-      <c r="J130" s="8" t="n"/>
-      <c r="K130" s="8" t="n"/>
-      <c r="L130" s="8" t="n"/>
-      <c r="M130" s="8" t="n"/>
-      <c r="N130" s="8" t="n"/>
+      <c r="I130" s="9" t="inlineStr">
+        <is>
+          <t>АО «Энергия»</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="inlineStr">
+        <is>
+          <t>7805499441</t>
+        </is>
+      </c>
+      <c r="K130" s="9" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="L130" s="9" t="inlineStr">
+        <is>
+          <t>10743786</t>
+        </is>
+      </c>
+      <c r="M130" s="9" t="inlineStr">
+        <is>
+          <t>08.12.2030</t>
+        </is>
+      </c>
+      <c r="N130" s="9" t="inlineStr">
+        <is>
+          <t>Клапан обратный двухстворчатый межфланцевый тип 010C</t>
+        </is>
+      </c>
       <c r="O130" s="8" t="n"/>
     </row>
     <row r="131" ht="52" customHeight="1">
@@ -6069,12 +6101,36 @@
       <c r="H131" s="7" t="n">
         <v>14760.17</v>
       </c>
-      <c r="I131" s="8" t="n"/>
-      <c r="J131" s="8" t="n"/>
-      <c r="K131" s="8" t="n"/>
-      <c r="L131" s="8" t="n"/>
-      <c r="M131" s="8" t="n"/>
-      <c r="N131" s="8" t="n"/>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>АО «Энергия»</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="inlineStr">
+        <is>
+          <t>7805499441</t>
+        </is>
+      </c>
+      <c r="K131" s="9" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="L131" s="9" t="inlineStr">
+        <is>
+          <t>10743786</t>
+        </is>
+      </c>
+      <c r="M131" s="9" t="inlineStr">
+        <is>
+          <t>08.12.2030</t>
+        </is>
+      </c>
+      <c r="N131" s="9" t="inlineStr">
+        <is>
+          <t>Клапан обратный двухстворчатый межфланцевый тип 010C</t>
+        </is>
+      </c>
       <c r="O131" s="8" t="n"/>
     </row>
     <row r="132" ht="52" customHeight="1">
@@ -6155,12 +6211,36 @@
       <c r="H133" s="7" t="n">
         <v>12109.11</v>
       </c>
-      <c r="I133" s="8" t="n"/>
-      <c r="J133" s="8" t="n"/>
-      <c r="K133" s="8" t="n"/>
-      <c r="L133" s="8" t="n"/>
-      <c r="M133" s="8" t="n"/>
-      <c r="N133" s="8" t="n"/>
+      <c r="I133" s="9" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ»</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="inlineStr">
+        <is>
+          <t>7718625072</t>
+        </is>
+      </c>
+      <c r="K133" s="9" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="L133" s="9" t="inlineStr">
+        <is>
+          <t>10618660</t>
+        </is>
+      </c>
+      <c r="M133" s="9" t="inlineStr">
+        <is>
+          <t>17.03.2028</t>
+        </is>
+      </c>
+      <c r="N133" s="9" t="inlineStr">
+        <is>
+          <t>Клапаны обратные торговой марки «Гранлок", тип ЗОП , DN 150 мм , PN 16 бар»</t>
+        </is>
+      </c>
       <c r="O133" s="8" t="n"/>
     </row>
     <row r="134" ht="52" customHeight="1">
@@ -7359,12 +7439,36 @@
       <c r="H161" s="7" t="n">
         <v>73960.67</v>
       </c>
-      <c r="I161" s="8" t="n"/>
-      <c r="J161" s="8" t="n"/>
-      <c r="K161" s="8" t="n"/>
-      <c r="L161" s="8" t="n"/>
-      <c r="M161" s="8" t="n"/>
-      <c r="N161" s="8" t="n"/>
+      <c r="I161" s="9" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш»</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="inlineStr">
+        <is>
+          <t>0323085570</t>
+        </is>
+      </c>
+      <c r="K161" s="9" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="L161" s="9" t="inlineStr">
+        <is>
+          <t>10789125</t>
+        </is>
+      </c>
+      <c r="M161" s="9" t="inlineStr">
+        <is>
+          <t>30.06.2031</t>
+        </is>
+      </c>
+      <c r="N161" s="9" t="inlineStr">
+        <is>
+          <t>Регуляторы давления, перепада давления, расхода, перепуска УРРД DN 15-300; PN 16-40</t>
+        </is>
+      </c>
       <c r="O161" s="8" t="n"/>
     </row>
     <row r="162" ht="52" customHeight="1">
@@ -7445,12 +7549,36 @@
       <c r="H163" s="7" t="n">
         <v>89689.52</v>
       </c>
-      <c r="I163" s="8" t="n"/>
-      <c r="J163" s="8" t="n"/>
-      <c r="K163" s="8" t="n"/>
-      <c r="L163" s="8" t="n"/>
-      <c r="M163" s="8" t="n"/>
-      <c r="N163" s="8" t="n"/>
+      <c r="I163" s="9" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш»</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="inlineStr">
+        <is>
+          <t>0323085570</t>
+        </is>
+      </c>
+      <c r="K163" s="9" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="L163" s="9" t="inlineStr">
+        <is>
+          <t>10789125</t>
+        </is>
+      </c>
+      <c r="M163" s="9" t="inlineStr">
+        <is>
+          <t>30.06.2031</t>
+        </is>
+      </c>
+      <c r="N163" s="9" t="inlineStr">
+        <is>
+          <t>Регуляторы давления, перепада давления, расхода, перепуска УРРД DN 15-300; PN 16-40</t>
+        </is>
+      </c>
       <c r="O163" s="8" t="n"/>
     </row>
     <row r="164" ht="52" customHeight="1">
@@ -7488,12 +7616,36 @@
       <c r="H164" s="7" t="n">
         <v>177103.13</v>
       </c>
-      <c r="I164" s="8" t="n"/>
-      <c r="J164" s="8" t="n"/>
-      <c r="K164" s="8" t="n"/>
-      <c r="L164" s="8" t="n"/>
-      <c r="M164" s="8" t="n"/>
-      <c r="N164" s="8" t="n"/>
+      <c r="I164" s="9" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш»</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="inlineStr">
+        <is>
+          <t>0323085570</t>
+        </is>
+      </c>
+      <c r="K164" s="9" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="L164" s="9" t="inlineStr">
+        <is>
+          <t>10789125</t>
+        </is>
+      </c>
+      <c r="M164" s="9" t="inlineStr">
+        <is>
+          <t>30.06.2031</t>
+        </is>
+      </c>
+      <c r="N164" s="9" t="inlineStr">
+        <is>
+          <t>Регуляторы давления, перепада давления, расхода, перепуска УРРД DN 15-300; PN 16-40</t>
+        </is>
+      </c>
       <c r="O164" s="8" t="n"/>
     </row>
     <row r="165" ht="52" customHeight="1">
@@ -7703,12 +7855,36 @@
       <c r="H169" s="7" t="n">
         <v>89689.52</v>
       </c>
-      <c r="I169" s="8" t="n"/>
-      <c r="J169" s="8" t="n"/>
-      <c r="K169" s="8" t="n"/>
-      <c r="L169" s="8" t="n"/>
-      <c r="M169" s="8" t="n"/>
-      <c r="N169" s="8" t="n"/>
+      <c r="I169" s="9" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш»</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="inlineStr">
+        <is>
+          <t>0323085570</t>
+        </is>
+      </c>
+      <c r="K169" s="9" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="L169" s="9" t="inlineStr">
+        <is>
+          <t>10789125</t>
+        </is>
+      </c>
+      <c r="M169" s="9" t="inlineStr">
+        <is>
+          <t>30.06.2031</t>
+        </is>
+      </c>
+      <c r="N169" s="9" t="inlineStr">
+        <is>
+          <t>Регуляторы давления, перепада давления, расхода, перепуска УРРД DN 15-300; PN 16-40</t>
+        </is>
+      </c>
       <c r="O169" s="8" t="n"/>
     </row>
   </sheetData>
